--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08.09.2026 16:45</t>
+          <t>09.09.2026 00:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:42</t>
+          <t>09.09.2026 00:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 00:54</t>
+          <t>09.09.2026 01:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:16</t>
+          <t>09.09.2026 01:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 01:33</t>
+          <t>09.09.2026 04:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 04:58</t>
+          <t>09.09.2026 05:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:10</t>
+          <t>09.09.2026 05:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:20</t>
+          <t>09.09.2026 05:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="49" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -1049,17 +1049,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Поблагодарил коллегу за помощь</t>
+          <t>За что вы поблагодарили коллегу: Ответ на шаг 2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>проба</t>
+          <t>За что вы поблагодарили коллегу: Ответ на шаг 2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 05:52</t>
+          <t>09.09.2026 06:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 06:34</t>
+          <t>09.09.2026 09:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 09:17</t>
+          <t>09.09.2026 10:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:01</t>
+          <t>09.09.2026 10:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 10:53</t>
+          <t>09.09.2026 12:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:27</t>
+          <t>09.09.2026 12:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:32</t>
+          <t>09.09.2026 12:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:41</t>
+          <t>09.09.2026 12:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:48</t>
+          <t>09.09.2026 12:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 12:54</t>
+          <t>09.09.2026 13:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:08</t>
+          <t>09.09.2026 13:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 13:18</t>
+          <t>09.09.2026 15:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:19</t>
+          <t>09.09.2026 15:23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -516,12 +516,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,50 +538,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>TG id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Команда</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Баллы</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Модерация (кто)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Модерация (когда)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Причина отклонения</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Причина дисквалификации</t>
         </is>
@@ -597,38 +603,38 @@
           <t>user0</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1000</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Добряки</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>200</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>999</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -643,38 +649,38 @@
           <t>user1</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1001</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Добряки</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>999</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -689,38 +695,38 @@
           <t>user2</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1002</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Добряки</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>999</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -735,38 +741,38 @@
           <t>user3</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1003</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Добряки</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>999</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -781,38 +787,38 @@
           <t>user4</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1004</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Добряки</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>999</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -827,38 +833,38 @@
           <t>user5</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1005</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Лучики</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>999</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -873,38 +879,38 @@
           <t>user6</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1006</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Алматы</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Лучики</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>registered</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>999</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>09.09.2026 15:23</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1060,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1112,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1170,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1230,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1247,7 +1253,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1270,7 +1276,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 15:23</t>
+          <t>09.09.2026 16:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/data/smoke_export.xlsx
+++ b/data/smoke_export.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.09.2026 16:42</t>
+          <t>09.09.2026 16:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
